--- a/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
+++ b/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
   <si>
     <t>Translator notes</t>
   </si>
@@ -64,13 +64,7 @@
     <t>compliance.statementSuccess.components.success.confirmationEmail</t>
   </si>
   <si>
-    <t>We have sent a confirmation email to: {{userEmail}}</t>
-  </si>
-  <si>
-    <t>compliance.statementSuccess.components.success.publicRegisterBullet2</t>
-  </si>
-  <si>
-    <t>submitted your statement of compliance</t>
+    <t>We have sent a confirmation email to: {{userEmail}}.</t>
   </si>
   <si>
     <t>compliance.statementSuccess.components.success.regulatorBullet2</t>
@@ -481,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -632,28 +626,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:F11"/>
+  <autoFilter ref="A5:F10"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>

--- a/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
+++ b/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
   <si>
     <t>Translator notes</t>
   </si>
@@ -55,6 +55,9 @@
     <t/>
   </si>
   <si>
+    <t>https://www.figma.com/design/eG3Z7k6gmh9ZCtooRy0iBz/Certificate-Statement-of-Certification?node-id=4297-37093&amp;t=i61f1BsSBR1bSqaq-4</t>
+  </si>
+  <si>
     <t>compliance.statementSuccess.panelTitle</t>
   </si>
   <si>
@@ -67,6 +70,18 @@
     <t>We have sent a confirmation email to: {{userEmail}}.</t>
   </si>
   <si>
+    <t>compliance.components.success.statementLinkLead</t>
+  </si>
+  <si>
+    <t>You will find a link to your statement of compliance at the bottom of the</t>
+  </si>
+  <si>
+    <t>compliance.components.success.statementLinkSuffix</t>
+  </si>
+  <si>
+    <t>page.</t>
+  </si>
+  <si>
     <t>compliance.statementSuccess.components.success.regulatorBullet2</t>
   </si>
   <si>
@@ -76,7 +91,13 @@
     <t>compliance.statementSuccess.components.success.resubmitLead</t>
   </si>
   <si>
-    <t>If you need to resubmit your statement of compliance, contact the {{regulatorName}}:</t>
+    <t>If you need to resubmit your statement of compliance, contact {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>compliance.components.success.viewStatementButton</t>
+  </si>
+  <si>
+    <t>View your statement</t>
   </si>
 </sst>
 </file>
@@ -475,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
@@ -526,7 +547,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -543,12 +564,12 @@
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -557,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>13</v>
@@ -568,7 +589,7 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -577,7 +598,7 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>13</v>
@@ -588,7 +609,7 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -597,7 +618,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>13</v>
@@ -608,7 +629,7 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -617,7 +638,7 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>13</v>
@@ -626,13 +647,76 @@
         <v>13</v>
       </c>
     </row>
+    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:F10"/>
+  <autoFilter ref="A5:F13"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D3:F3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
+++ b/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3BAF86-DBEB-428A-9654-20C07AEBECCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
+    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>Translator notes</t>
   </si>
@@ -98,27 +102,59 @@
   </si>
   <si>
     <t>View your statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the Figma file for the full page content. Text that is repeated within the service may be translated in another file and omitted here. </t>
+  </si>
+  <si>
+    <t>Wedi cyflwyno’r datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>Rydym wedi anfon e-bost cadarnhau at: {{userEmail}}.</t>
+  </si>
+  <si>
+    <t>Bydd dolen at eich datganiad cydymffurfio ar waelod y</t>
+  </si>
+  <si>
+    <t>dudalen.</t>
+  </si>
+  <si>
+    <t>ailgyflwyno eich datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>Os oes angen i chi ailgyflwyno eich datganiad cydymffurfio, cysylltwch â {{regulatorName}}:</t>
+  </si>
+  <si>
+    <t>Gweld eich datganiad</t>
+  </si>
+  <si>
+    <t>Rydych wedi cyflwyno eich datganiad cydymffurfio ar gyfer {{year}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -146,15 +182,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -495,9 +537,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -505,71 +547,56 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -578,18 +605,18 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -598,18 +625,18 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -618,18 +645,18 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -638,18 +665,18 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -658,18 +685,18 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -678,18 +705,18 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -698,26 +725,46 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="14" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:F13"/>
+  <autoFilter ref="A6:F14" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F6" r:id="rId1"/>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
+++ b/translations/welsh-translations/xlsx/13-cso-statement-success.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3BAF86-DBEB-428A-9654-20C07AEBECCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Welsh translations" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Welsh translations" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
   <si>
     <t>Translator notes</t>
   </si>
@@ -56,105 +52,97 @@
     <t>Statement of compliance submitted</t>
   </si>
   <si>
+    <t>Wedi cyflwyno’r datganiad cydymffurfio</t>
+  </si>
+  <si>
+    <t>https://www.figma.com/design/eG3Z7k6gmh9ZCtooRy0iBz/Certificate-Statement-of-Certification?node-id=4297-37093&amp;t=i61f1BsSBR1bSqaq-4</t>
+  </si>
+  <si>
+    <t>compliance.statementSuccess.panelTitle</t>
+  </si>
+  <si>
+    <t>You have submitted your {{year}} statement of compliance</t>
+  </si>
+  <si>
+    <t>Rydych wedi cyflwyno eich datganiad cydymffurfio ar gyfer {{year}}</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>https://www.figma.com/design/eG3Z7k6gmh9ZCtooRy0iBz/Certificate-Statement-of-Certification?node-id=4297-37093&amp;t=i61f1BsSBR1bSqaq-4</t>
-  </si>
-  <si>
-    <t>compliance.statementSuccess.panelTitle</t>
-  </si>
-  <si>
-    <t>You have submitted your {{year}} statement of compliance</t>
-  </si>
-  <si>
     <t>compliance.statementSuccess.components.success.confirmationEmail</t>
   </si>
   <si>
     <t>We have sent a confirmation email to: {{userEmail}}.</t>
   </si>
   <si>
+    <t>Rydym wedi anfon e-bost cadarnhau at: {{userEmail}}.</t>
+  </si>
+  <si>
     <t>compliance.components.success.statementLinkLead</t>
   </si>
   <si>
     <t>You will find a link to your statement of compliance at the bottom of the</t>
   </si>
   <si>
+    <t>Bydd dolen at eich datganiad cydymffurfio ar waelod y</t>
+  </si>
+  <si>
     <t>compliance.components.success.statementLinkSuffix</t>
   </si>
   <si>
     <t>page.</t>
   </si>
   <si>
+    <t>dudalen.</t>
+  </si>
+  <si>
     <t>compliance.statementSuccess.components.success.regulatorBullet2</t>
   </si>
   <si>
     <t>resubmit your statement of compliance</t>
   </si>
   <si>
+    <t>ailgyflwyno eich datganiad cydymffurfio</t>
+  </si>
+  <si>
     <t>compliance.statementSuccess.components.success.resubmitLead</t>
   </si>
   <si>
     <t>If you need to resubmit your statement of compliance, contact {{regulatorName}}:</t>
   </si>
   <si>
+    <t>Os oes angen i chi ailgyflwyno eich datganiad cydymffurfio, cysylltwch â {{regulatorName}}:</t>
+  </si>
+  <si>
     <t>compliance.components.success.viewStatementButton</t>
   </si>
   <si>
     <t>View your statement</t>
   </si>
   <si>
-    <t xml:space="preserve">Check the Figma file for the full page content. Text that is repeated within the service may be translated in another file and omitted here. </t>
-  </si>
-  <si>
-    <t>Wedi cyflwyno’r datganiad cydymffurfio</t>
-  </si>
-  <si>
-    <t>Rydym wedi anfon e-bost cadarnhau at: {{userEmail}}.</t>
-  </si>
-  <si>
-    <t>Bydd dolen at eich datganiad cydymffurfio ar waelod y</t>
-  </si>
-  <si>
-    <t>dudalen.</t>
-  </si>
-  <si>
-    <t>ailgyflwyno eich datganiad cydymffurfio</t>
-  </si>
-  <si>
-    <t>Os oes angen i chi ailgyflwyno eich datganiad cydymffurfio, cysylltwch â {{regulatorName}}:</t>
-  </si>
-  <si>
     <t>Gweld eich datganiad</t>
-  </si>
-  <si>
-    <t>Rydych wedi cyflwyno eich datganiad cydymffurfio ar gyfer {{year}}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -182,21 +170,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -537,9 +519,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" hidden="1" customWidth="1"/>
     <col min="2" max="3" width="35" hidden="1" customWidth="1"/>
@@ -547,56 +529,71 @@
     <col min="6" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="3" t="s">
+    <row r="1" ht="24" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D2" s="4" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="4:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="81.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="82" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -605,18 +602,18 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
@@ -625,18 +622,18 @@
         <v>11</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -645,18 +642,18 @@
         <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
@@ -665,18 +662,18 @@
         <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -685,18 +682,18 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -705,18 +702,18 @@
         <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -725,46 +722,26 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="5" t="s">
         <v>35</v>
       </c>
+      <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:F14" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:F13"/>
   <mergeCells count="3">
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D3:F3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F6" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>